--- a/planning/gantt 1 (1).xlsx
+++ b/planning/gantt 1 (1).xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29421"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\Cours\INFOB318  - Projet individuel\INFOB318-template\planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66AFC4A1-B751-4E62-84A1-4B28BEC7E1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17040" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="effort" sheetId="1" r:id="rId1"/>
+    <sheet name="effort" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Nom:</t>
   </si>
@@ -107,14 +107,26 @@
     <t>Maitriser les bases du JAX avant le 3/11</t>
   </si>
   <si>
-    <t>Maitriser les bases du Kernel tuning etc</t>
+    <t>Maitriser JAX 101 avant le 15/11</t>
+  </si>
+  <si>
+    <t>Comprendre le gradient descent etc.. </t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>jup notebook x svm scratch, sub 15nov</t>
+  </si>
+  <si>
+    <t>0,30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,11 +135,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -175,8 +186,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,319 +202,65 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="4" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="5" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.4998399913311"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="0" tint="-0.149859994649887"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="29">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -513,111 +276,599 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
     <border>
       <left/>
       <right/>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="6" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="3" xfId="6" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="6" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="7" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="9" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="22" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="19" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="21" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="8" borderId="23" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="5" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="10" applyFont="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="20 % - Accent1" xfId="1" builtinId="30"/>
-    <cellStyle name="60 % - Accent2" xfId="3" builtinId="36"/>
-    <cellStyle name="Accent2" xfId="2" builtinId="33"/>
-    <cellStyle name="Accent3" xfId="4" builtinId="37"/>
-    <cellStyle name="Commentaire" xfId="5" builtinId="10"/>
+  <cellStyles count="11">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
+    <cellStyle name="20 % - Accent1" xfId="6" builtinId="30"/>
+    <cellStyle name="Accent2" xfId="7" builtinId="33"/>
+    <cellStyle name="60 % - Accent2" xfId="8" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="9" builtinId="37"/>
+    <cellStyle name="Commentaire" xfId="10" builtinId="10"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf/>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <u val="none"/>
+        <strike val="0"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -915,21 +1166,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:AH46"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="11.4242857142857" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="21.7142857142857" customWidth="1"/>
+    <col min="4" max="7" width="11.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7142857142857" customWidth="1"/>
+    <col min="11" max="16" width="11.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7142857142857" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:34" ht="21">
+    <row r="2" spans="2:7" ht="21">
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
@@ -941,7 +1192,7 @@
       <c r="F2" s="28"/>
       <c r="G2" s="28"/>
     </row>
-    <row r="3" spans="2:34" ht="21">
+    <row r="3" spans="2:7" ht="21">
       <c r="B3" s="21" t="s">
         <v>2</v>
       </c>
@@ -953,7 +1204,7 @@
       <c r="F3" s="28"/>
       <c r="G3" s="28"/>
     </row>
-    <row r="4" spans="2:34" ht="21">
+    <row r="4" spans="2:7" ht="21">
       <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
@@ -965,7 +1216,7 @@
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
     </row>
-    <row r="5" spans="2:34" ht="21">
+    <row r="5" spans="2:7" ht="21">
       <c r="B5" s="21" t="s">
         <v>6</v>
       </c>
@@ -977,8 +1228,8 @@
       <c r="F5" s="28"/>
       <c r="G5" s="28"/>
     </row>
-    <row r="6" spans="2:34" ht="15" thickBot="1"/>
-    <row r="7" spans="2:34" ht="15" thickBot="1">
+    <row r="6" ht="15" thickBot="1"/>
+    <row r="7" spans="3:34" ht="15" thickBot="1">
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
@@ -987,16 +1238,16 @@
         <v>4</v>
       </c>
       <c r="E7" s="20">
-        <f t="shared" ref="E7:Z7" si="0">SUM(E11:E36)</f>
+        <f t="shared" si="0" ref="E7:Z7">SUM(E11:E36)</f>
         <v>4</v>
       </c>
       <c r="F7" s="20">
         <f t="shared" si="0"/>
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G7" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
@@ -1075,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="AA7" s="6">
-        <f t="shared" ref="AA7:AH7" si="1">SUM(AA11:AA36)</f>
+        <f t="shared" si="1" ref="AA7:AH7">SUM(AA11:AA36)</f>
         <v>0</v>
       </c>
       <c r="AB7" s="6">
@@ -1125,7 +1376,7 @@
         <v>45957</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" ref="G8:Q8" si="2">F8+7</f>
+        <f t="shared" si="2" ref="G8:Q8">F8+7</f>
         <v>45964</v>
       </c>
       <c r="H8" s="2">
@@ -1169,39 +1420,39 @@
         <v>46034</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" ref="R8" si="3">Q8+7</f>
+        <f t="shared" si="3" ref="R8">Q8+7</f>
         <v>46041</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" ref="S8" si="4">R8+7</f>
+        <f t="shared" si="4" ref="S8">R8+7</f>
         <v>46048</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" ref="T8" si="5">S8+7</f>
+        <f t="shared" si="5" ref="T8">S8+7</f>
         <v>46055</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" ref="U8" si="6">T8+7</f>
+        <f t="shared" si="6" ref="U8">T8+7</f>
         <v>46062</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" ref="V8" si="7">U8+7</f>
+        <f t="shared" si="7" ref="V8">U8+7</f>
         <v>46069</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" ref="W8" si="8">V8+7</f>
+        <f t="shared" si="8" ref="W8">V8+7</f>
         <v>46076</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" ref="X8" si="9">W8+7</f>
+        <f t="shared" si="9" ref="X8">W8+7</f>
         <v>46083</v>
       </c>
       <c r="Y8" s="3">
-        <f t="shared" ref="Y8" si="10">X8+7</f>
+        <f t="shared" si="10" ref="Y8">X8+7</f>
         <v>46090</v>
       </c>
       <c r="Z8" s="3">
-        <f t="shared" ref="Z8:AH8" si="11">Y8+7</f>
+        <f t="shared" si="11" ref="Z8:AH8">Y8+7</f>
         <v>46097</v>
       </c>
       <c r="AA8" s="3">
@@ -1243,23 +1494,23 @@
       </c>
       <c r="C9" s="22">
         <f>SUM(C10:C46)</f>
-        <v>13.899999999999999</v>
+        <v>15</v>
       </c>
       <c r="D9" s="26">
         <f>SUM(D10:D46)</f>
         <v>4</v>
       </c>
       <c r="E9" s="26">
-        <f t="shared" ref="E9:Z9" si="12">SUM(E10:E46)</f>
+        <f t="shared" si="12" ref="E9:Z9">SUM(E10:E46)</f>
         <v>4</v>
       </c>
       <c r="F9" s="26">
         <f t="shared" si="12"/>
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G9" s="26">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="26">
         <f t="shared" si="12"/>
@@ -1338,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="26">
-        <f t="shared" ref="AA9:AH9" si="13">SUM(AA10:AA46)</f>
+        <f t="shared" si="13" ref="AA9:AH9">SUM(AA10:AA46)</f>
         <v>0</v>
       </c>
       <c r="AB9" s="26">
@@ -1415,14 +1666,16 @@
         <v>13</v>
       </c>
       <c r="C11" s="25">
-        <f t="shared" ref="C11:C46" si="14">SUM(D11:AH11)</f>
+        <f t="shared" si="14" ref="C11:C46">SUM(D11:AH11)</f>
         <v>1.2</v>
       </c>
       <c r="D11" s="17">
-        <v>1.2</v>
+        <v>1.20</v>
       </c>
       <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="F11" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -1458,10 +1711,10 @@
       </c>
       <c r="C12" s="25">
         <f t="shared" si="14"/>
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="D12" s="17">
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
@@ -1500,10 +1753,10 @@
       </c>
       <c r="C13" s="25">
         <f t="shared" si="14"/>
-        <v>0.2</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="D13" s="17">
-        <v>0.2</v>
+        <v>0.20</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1662,17 +1915,15 @@
       </c>
       <c r="C17" s="25">
         <f t="shared" si="14"/>
-        <v>7.3</v>
+        <v>5.2999999999999998</v>
       </c>
       <c r="D17" s="17">
-        <v>1.3</v>
+        <v>1.30</v>
       </c>
       <c r="E17" s="12">
         <v>4</v>
       </c>
-      <c r="F17" s="12">
-        <v>2</v>
-      </c>
+      <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -1708,13 +1959,15 @@
       </c>
       <c r="C18" s="25">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="17">
         <v>1</v>
       </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="F18" s="12">
+        <v>2</v>
+      </c>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -1750,12 +2003,12 @@
       </c>
       <c r="C19" s="25">
         <f t="shared" si="14"/>
-        <v>2.4500000000000002</v>
+        <v>3</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12">
-        <v>2.4500000000000002</v>
+        <v>3</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
@@ -1792,12 +2045,12 @@
       </c>
       <c r="C20" s="25">
         <f t="shared" si="14"/>
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="D20" s="17"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
@@ -1828,48 +2081,52 @@
       <c r="AG20" s="13"/>
       <c r="AH20" s="13"/>
     </row>
-    <row r="21" spans="2:34" ht="15" thickBot="1">
-      <c r="B21" s="7" t="s">
+    <row r="21" spans="2:34" ht="15" customHeight="1" thickBot="1">
+      <c r="B21" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="30">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="13"/>
-      <c r="AC21" s="13"/>
-      <c r="AD21" s="13"/>
-      <c r="AE21" s="13"/>
-      <c r="AF21" s="13"/>
-      <c r="AG21" s="13"/>
-      <c r="AH21" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33">
+        <v>1</v>
+      </c>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="34"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="35"/>
+      <c r="AD21" s="35"/>
+      <c r="AE21" s="35"/>
+      <c r="AF21" s="35"/>
+      <c r="AG21" s="35"/>
+      <c r="AH21" s="35"/>
     </row>
     <row r="22" spans="2:34" ht="15" thickBot="1">
-      <c r="B22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="C22" s="25">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -1877,7 +2134,9 @@
       <c r="D22" s="17"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
@@ -1907,7 +2166,9 @@
       <c r="AH22" s="13"/>
     </row>
     <row r="23" spans="2:34" ht="15" thickBot="1">
-      <c r="B23" s="7"/>
+      <c r="B23" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="C23" s="25">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -2826,7 +3087,7 @@
     <mergeCell ref="C5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
-    <cfRule type="dataBar" priority="73">
+    <cfRule type="dataBar" priority="150" dxfId="1">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2834,13 +3095,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AD0E4649-9E72-4706-9164-C3BAE99F2B77}</x14:id>
+          <x14:id>{449726de-1791-4040-bd03-89389f615c9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10:C46">
-    <cfRule type="dataBar" priority="3">
+    <cfRule type="dataBar" priority="149" dxfId="1">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2848,13 +3109,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A2C7A50C-F572-416B-9495-8A28D149BC35}</x14:id>
+          <x14:id>{6bf5b3cb-333e-4ae9-93a9-b5d9ac4340ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:C46">
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="148" dxfId="1">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2862,83 +3123,83 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91046929-9F97-4C47-9B86-AC798F7EDAC7}</x14:id>
+          <x14:id>{f2a06724-30d0-4522-a678-8922913ed44c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D11:P18 D21:P29 D19:H20 J19:P20">
-    <cfRule type="colorScale" priority="79">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+  <conditionalFormatting sqref="D11:P18 D19:H20 J19:P20 D21:P29">
+    <cfRule type="colorScale" priority="147" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:P30">
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="146" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:P35">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="145" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D36:P40">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="144" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D41:P41">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="143" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D42:P46">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="142" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10:Q10 Q11:Q29">
-    <cfRule type="colorScale" priority="76">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="141" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:AH9">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="140" dxfId="1">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2946,619 +3207,619 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BCD65580-FCE2-4CC5-9CCE-B782BE912BFA}</x14:id>
+          <x14:id>{e35bf5b2-0faa-497d-b40b-c015a744278a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10:AH46">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="139" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q30">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="138" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q31:Q35">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="137" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q36:Q40">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="136" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q41">
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="135" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q42:Q46">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="134" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:Z29">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="133" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R30:Z30">
-    <cfRule type="colorScale" priority="69">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="132" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R31:Z35">
-    <cfRule type="colorScale" priority="65">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="131" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R36:Z40">
-    <cfRule type="colorScale" priority="61">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="130" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R41:Z41">
-    <cfRule type="colorScale" priority="57">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="129" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R42:Z46">
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="128" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AA29">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="127" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA30">
-    <cfRule type="colorScale" priority="51">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="126" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA31:AA35">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="125" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA36:AA40">
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="124" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA41">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="123" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA42:AA46">
-    <cfRule type="colorScale" priority="47">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="122" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB10:AB29">
-    <cfRule type="colorScale" priority="46">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="121" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB30">
-    <cfRule type="colorScale" priority="45">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="120" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB31:AB35">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="119" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB36:AB40">
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="118" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB41">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="117" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB42:AB46">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="116" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC10:AC29">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="115" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC30">
-    <cfRule type="colorScale" priority="39">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="114" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC31:AC35">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="113" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC36:AC40">
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="112" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC41">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="111" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC42:AC46">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="110" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD10:AD29">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="109" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD30">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="108" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD31:AD35">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="107" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD36:AD40">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="106" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD41">
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="105" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD42:AD46">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="104" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE10:AE29">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="103" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE30">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="102" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE31:AE35">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="101" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE36:AE40">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="100" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE41">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="99" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE42:AE46">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="98" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF10:AF29">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="97" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF30">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="96" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF31:AF35">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="95" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF36:AF40">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="94" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF41">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="93" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF42:AF46">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="92" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG10:AG29">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="91" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG30">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="90" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG31:AG35">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="89" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG36:AG40">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="88" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG41">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="87" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG42:AG46">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="86" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH10:AH29">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="85" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH30">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="84" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH31:AH35">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="83" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH36:AH40">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="82" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH41">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="81" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH42:AH46">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+    <cfRule type="colorScale" priority="80" dxfId="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AD0E4649-9E72-4706-9164-C3BAE99F2B77}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+          <x14:cfRule type="dataBar" id="{449726de-1791-4040-bd03-89389f615c9d}">
+            <x14:dataBar minLength="10" maxLength="90" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:borderColor rgb="FFFFB628"/>
@@ -3566,23 +3827,45 @@
               <x14:negativeBorderColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
+            <x14:dxf>
+              <font>
+                <b val="0"/>
+                <i val="0"/>
+                <u val="none"/>
+                <strike val="0"/>
+                <sz val="11"/>
+                <name val="Calibri"/>
+                <color rgb="FF000000"/>
+              </font>
+            </x14:dxf>
           </x14:cfRule>
           <xm:sqref>C10</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A2C7A50C-F572-416B-9495-8A28D149BC35}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+          <x14:cfRule type="dataBar" id="{6bf5b3cb-333e-4ae9-93a9-b5d9ac4340ba}">
+            <x14:dataBar minLength="10" maxLength="90" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
+            <x14:dxf>
+              <font>
+                <b val="0"/>
+                <i val="0"/>
+                <u val="none"/>
+                <strike val="0"/>
+                <sz val="11"/>
+                <name val="Calibri"/>
+                <color rgb="FF000000"/>
+              </font>
+            </x14:dxf>
           </x14:cfRule>
           <xm:sqref>C10:C46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{91046929-9F97-4C47-9B86-AC798F7EDAC7}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+          <x14:cfRule type="dataBar" id="{f2a06724-30d0-4522-a678-8922913ed44c}">
+            <x14:dataBar minLength="10" maxLength="90" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:borderColor rgb="FFFFB628"/>
@@ -3590,17 +3873,39 @@
               <x14:negativeBorderColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
+            <x14:dxf>
+              <font>
+                <b val="0"/>
+                <i val="0"/>
+                <u val="none"/>
+                <strike val="0"/>
+                <sz val="11"/>
+                <name val="Calibri"/>
+                <color rgb="FF000000"/>
+              </font>
+            </x14:dxf>
           </x14:cfRule>
           <xm:sqref>C11:C46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BCD65580-FCE2-4CC5-9CCE-B782BE912BFA}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+          <x14:cfRule type="dataBar" id="{e35bf5b2-0faa-497d-b40b-c015a744278a}">
+            <x14:dataBar minLength="10" maxLength="90" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:negativeFillColor rgb="FFFF0000"/>
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
+            <x14:dxf>
+              <font>
+                <b val="0"/>
+                <i val="0"/>
+                <u val="none"/>
+                <strike val="0"/>
+                <sz val="11"/>
+                <name val="Calibri"/>
+                <color rgb="FF000000"/>
+              </font>
+            </x14:dxf>
           </x14:cfRule>
           <xm:sqref>D9:AH9</xm:sqref>
         </x14:conditionalFormatting>
